--- a/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
+++ b/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:30:17+00:00</t>
+    <t>2025-10-07T21:05:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1073,7 +1073,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="30.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="35.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="39.13671875" customWidth="true" bestFit="true"/>
@@ -2599,7 +2599,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>157</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>162</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>163</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>166</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>171</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>176</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>181</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>185</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>191</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>195</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>199</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>204</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>207</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>211</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>216</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>218</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>221</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>226</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>228</v>
       </c>
@@ -8939,12 +8939,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL73">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
+++ b/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:05:34+00:00</t>
+    <t>2025-11-21T23:55:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
+++ b/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T23:55:27+00:00</t>
+    <t>2026-01-12T21:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
+++ b/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T21:43:07+00:00</t>
+    <t>2026-01-22T19:20:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
+++ b/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T19:20:19+00:00</t>
+    <t>2026-02-17T21:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
+++ b/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T21:23:45+00:00</t>
+    <t>2026-03-17T18:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
+++ b/release-branch/StructureDefinition-bc-metadata-parameter-async-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T18:19:20+00:00</t>
+    <t>2026-03-25T21:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
